--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486339_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486339_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.3547</v>
+        <v>5.3558</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9998</v>
+        <v>4.0625</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3549</v>
+        <v>1.2933</v>
       </c>
       <c r="G2" t="n">
         <v>3.915</v>
@@ -610,13 +610,13 @@
         <v>2.3926</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0705</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4132</v>
+        <v>0.4759</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3427</v>
+        <v>-0.4044</v>
       </c>
       <c r="V2" t="n">
         <v>2.2393</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.2424</v>
+        <v>4.0315</v>
       </c>
       <c r="E3" t="n">
-        <v>6.1435</v>
+        <v>4.8709</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9011</v>
+        <v>-0.8394</v>
       </c>
       <c r="G3" t="n">
         <v>3.8836</v>
@@ -688,13 +688,13 @@
         <v>2.8276</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4437</v>
+        <v>-0.7673</v>
       </c>
       <c r="T3" t="n">
-        <v>1.8963</v>
+        <v>0.6237</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.4526</v>
+        <v>-1.391</v>
       </c>
       <c r="V3" t="n">
         <v>-1.695</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4891</v>
+        <v>2.9787</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7896</v>
+        <v>4.1559</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.3005</v>
+        <v>-1.1772</v>
       </c>
       <c r="G4" t="n">
         <v>-0.3826</v>
@@ -766,13 +766,13 @@
         <v>3.0451</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.5209</v>
+        <v>-0.0312</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8099</v>
+        <v>0.5564</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7109</v>
+        <v>-0.5876</v>
       </c>
       <c r="V4" t="n">
         <v>0.5649999999999999</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3679</v>
+        <v>0.6484</v>
       </c>
       <c r="E5" t="n">
-        <v>2.8372</v>
+        <v>3.241</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.4693</v>
+        <v>-2.5926</v>
       </c>
       <c r="G5" t="n">
         <v>1.9604</v>
@@ -844,13 +844,13 @@
         <v>1.0875</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.3548</v>
+        <v>-1.0743</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1935</v>
+        <v>0.2103</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.1613</v>
+        <v>-1.2846</v>
       </c>
       <c r="V5" t="n">
         <v>-1.3252</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4746</v>
+        <v>-0.6181</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6445</v>
+        <v>1.3777</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.1191</v>
+        <v>-1.9958</v>
       </c>
       <c r="G6" t="n">
         <v>-2.3721</v>
@@ -922,13 +922,13 @@
         <v>1.305</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0498</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>1.1717</v>
+        <v>0.9049</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.1219</v>
+        <v>-0.9986</v>
       </c>
       <c r="V6" t="n">
         <v>0.7602</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. BOCCA</t>
+          <t>J. ARAMBURU LAMY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.681</v>
+        <v>-2.3636</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5603</v>
+        <v>-3.1885</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1206</v>
+        <v>0.8249</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.7789</v>
+        <v>-4.3807</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.2043</v>
+        <v>-0.7208</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.5746</v>
+        <v>-3.66</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.9255</v>
+        <v>-3.4196</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.4354</v>
+        <v>-1.4139</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.4901</v>
+        <v>-2.0057</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1466</v>
+        <v>-0.9611</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2311</v>
+        <v>0.6932</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.08450000000000001</v>
+        <v>-1.6543</v>
       </c>
       <c r="P7" t="n">
-        <v>0.435</v>
+        <v>1.305</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.305</v>
       </c>
       <c r="R7" t="n">
-        <v>0.435</v>
+        <v>2.6101</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8581</v>
+        <v>-0.2226</v>
       </c>
       <c r="T7" t="n">
-        <v>1.3651</v>
+        <v>0.4062</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.507</v>
+        <v>-0.6288</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1952</v>
+        <v>0.9347</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X7" t="n">
         <v>-0.1952</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. ARAMBURU LAMY</t>
+          <t>A. SCARIOLO ARES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.4629</v>
+        <v>-2.424</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.257</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7941</v>
+        <v>-2.495</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.3807</v>
+        <v>-2.3371</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7208</v>
+        <v>0.2679</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.66</v>
+        <v>-2.6049</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.4196</v>
+        <v>0.8257</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.4139</v>
+        <v>0.8823</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.0057</v>
+        <v>-0.0566</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9611</v>
+        <v>-3.1628</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6932</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.6543</v>
+        <v>-2.5484</v>
       </c>
       <c r="P8" t="n">
-        <v>1.305</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.305</v>
+        <v>-2.1751</v>
       </c>
       <c r="R8" t="n">
-        <v>2.6101</v>
+        <v>0.6525</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3219</v>
+        <v>1.0452</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3377</v>
+        <v>1.0299</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6596</v>
+        <v>0.0153</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9347</v>
+        <v>0.3904</v>
       </c>
       <c r="W8" t="n">
-        <v>1.13</v>
+        <v>0.3904</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. SCARIOLO ARES</t>
+          <t>J. BOCCA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.2826</v>
+        <v>-2.5442</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0033</v>
+        <v>-2.4544</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.2792</v>
+        <v>-0.0898</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.3371</v>
+        <v>-2.7789</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2679</v>
+        <v>-1.2043</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.6049</v>
+        <v>-1.5746</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8257</v>
+        <v>-2.9255</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8823</v>
+        <v>-1.4354</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0566</v>
+        <v>-1.4901</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.1628</v>
+        <v>0.1466</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6143999999999999</v>
+        <v>0.2311</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.5484</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.5225</v>
+        <v>0.435</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6525</v>
+        <v>0.435</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1866</v>
+        <v>-0.0051</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0445</v>
+        <v>0.4711</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2311</v>
+        <v>-0.4762</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3904</v>
+        <v>-0.1952</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3904</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.177</v>
+        <v>-3.4572</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6286</v>
+        <v>-1.0013</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.5484</v>
+        <v>-2.456</v>
       </c>
       <c r="G10" t="n">
         <v>-2.5773</v>
@@ -1234,13 +1234,13 @@
         <v>1.0875</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.4044</v>
+        <v>-0.6847</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3305</v>
+        <v>0.2968</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.074</v>
+        <v>-0.9815</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1952</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.7646</v>
+        <v>-4.3107</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.5566</v>
+        <v>-3.0411</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.208</v>
+        <v>-1.2697</v>
       </c>
       <c r="G11" t="n">
         <v>1.5644</v>
@@ -1312,13 +1312,13 @@
         <v>3.0451</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.6993</v>
+        <v>-2.2454</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1644</v>
+        <v>-0.6489</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.5348</v>
+        <v>-1.5965</v>
       </c>
       <c r="V11" t="n">
         <v>-3.1947</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.388599999999999</v>
+        <v>-2.703399999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>7.408799999999999</v>
+        <v>8.0937</v>
       </c>
       <c r="F12" t="n">
-        <v>-10.7972</v>
+        <v>-10.7973</v>
       </c>
       <c r="G12" t="n">
         <v>-3.5053</v>
@@ -1381,7 +1381,7 @@
         <v>-14.1087</v>
       </c>
       <c r="P12" t="n">
-        <v>6.5252</v>
+        <v>6.525200000000001</v>
       </c>
       <c r="Q12" t="n">
         <v>-11.9628</v>
@@ -1390,13 +1390,13 @@
         <v>18.488</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.692600000000001</v>
+        <v>-4.0076</v>
       </c>
       <c r="T12" t="n">
-        <v>3.6412</v>
+        <v>4.3263</v>
       </c>
       <c r="U12" t="n">
-        <v>-8.3337</v>
+        <v>-8.333900000000002</v>
       </c>
       <c r="V12" t="n">
         <v>-1.7157</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.4081</v>
+        <v>8.1853</v>
       </c>
       <c r="E13" t="n">
-        <v>7.0841</v>
+        <v>7.8664</v>
       </c>
       <c r="F13" t="n">
-        <v>0.324</v>
+        <v>0.3189</v>
       </c>
       <c r="G13" t="n">
         <v>7.1196</v>
@@ -1468,13 +1468,13 @@
         <v>2.1751</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8839</v>
+        <v>-0.1067</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4554</v>
+        <v>0.3269</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4284</v>
+        <v>-0.4335</v>
       </c>
       <c r="V13" t="n">
         <v>2.2599</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.8994</v>
+        <v>3.7633</v>
       </c>
       <c r="E14" t="n">
-        <v>4.2783</v>
+        <v>4.0548</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3789</v>
+        <v>-0.2915</v>
       </c>
       <c r="G14" t="n">
         <v>2.877</v>
@@ -1546,13 +1546,13 @@
         <v>1.305</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2826</v>
+        <v>-0.4188</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3461</v>
+        <v>0.1226</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6287</v>
+        <v>-0.5414</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8697</v>
+        <v>1.5537</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2983</v>
+        <v>1.0748</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5714</v>
+        <v>0.479</v>
       </c>
       <c r="G15" t="n">
         <v>2.0119</v>
@@ -1624,13 +1624,13 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9454</v>
+        <v>0.6294</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5516</v>
+        <v>0.3281</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3938</v>
+        <v>0.3013</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. GIL GARCIA</t>
+          <t>R. VILA SOLEY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1378</v>
+        <v>0.4856</v>
       </c>
       <c r="E16" t="n">
-        <v>3.3344</v>
+        <v>-0.4053</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.1966</v>
+        <v>0.891</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.6524</v>
+        <v>0.2459</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4532</v>
+        <v>-0.4107</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1992</v>
+        <v>0.6566</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2154</v>
+        <v>-0.1109</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.4348</v>
+        <v>-0.3404</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6502</v>
+        <v>0.2295</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8679</v>
+        <v>0.3568</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0184</v>
+        <v>-0.0703</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8495</v>
+        <v>0.4271</v>
       </c>
       <c r="P16" t="n">
-        <v>0.435</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R16" t="n">
         <v>0.435</v>
       </c>
       <c r="S16" t="n">
-        <v>2.29</v>
+        <v>0.8923</v>
       </c>
       <c r="T16" t="n">
-        <v>2.9237</v>
+        <v>0.7931</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6338</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.9347</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0654</v>
+        <v>0.2638</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4306</v>
+        <v>-1.3246</v>
       </c>
       <c r="F17" t="n">
-        <v>1.496</v>
+        <v>1.5884</v>
       </c>
       <c r="G17" t="n">
         <v>-1.3424</v>
@@ -1780,13 +1780,13 @@
         <v>1.7401</v>
       </c>
       <c r="S17" t="n">
-        <v>2.8003</v>
+        <v>1.9987</v>
       </c>
       <c r="T17" t="n">
-        <v>1.9167</v>
+        <v>1.0227</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8836000000000001</v>
+        <v>0.9761</v>
       </c>
       <c r="V17" t="n">
         <v>1.13</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. VILA SOLEY</t>
+          <t>G. GIL GARCIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1003</v>
+        <v>-0.4011</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8522999999999999</v>
+        <v>1.7698</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9526</v>
+        <v>-2.1709</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2459</v>
+        <v>-0.6524</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4107</v>
+        <v>-0.4532</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6566</v>
+        <v>-0.1992</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1109</v>
+        <v>0.2154</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3404</v>
+        <v>-0.4348</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2295</v>
+        <v>0.6502</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3568</v>
+        <v>-0.8679</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0703</v>
+        <v>-0.0184</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4271</v>
+        <v>-0.8495</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.6525</v>
+        <v>0.435</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0.435</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5069</v>
+        <v>0.7511</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3461</v>
+        <v>1.3591</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1608</v>
+        <v>-0.6081</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.9347</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.98</v>
+        <v>-0.4648</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4137</v>
+        <v>-1.0784</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4337</v>
+        <v>0.6135</v>
       </c>
       <c r="G19" t="n">
         <v>-1.0347</v>
@@ -1936,13 +1936,13 @@
         <v>0.87</v>
       </c>
       <c r="S19" t="n">
-        <v>0.077</v>
+        <v>0.5921</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0925</v>
+        <v>0.4278</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0155</v>
+        <v>0.1643</v>
       </c>
       <c r="V19" t="n">
         <v>0.1952</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. HUELVES GARCIA</t>
+          <t>R. SEOANE RODICIO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1153</v>
+        <v>-0.7191</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3906</v>
+        <v>-0.2151</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7247</v>
+        <v>-0.5041</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.5241</v>
+        <v>-1.3032</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.1655</v>
+        <v>-0.3988</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3586</v>
+        <v>-0.9044</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.8043</v>
+        <v>-0.2136</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.6147</v>
+        <v>0.2039</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.1896</v>
+        <v>-0.4175</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7197</v>
+        <v>-1.0896</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5508</v>
+        <v>-0.6027</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1689</v>
+        <v>-0.4869</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.9576</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.2626</v>
+        <v>-2.1751</v>
       </c>
       <c r="R20" t="n">
-        <v>1.305</v>
+        <v>1.5225</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9111</v>
+        <v>-0.0886</v>
       </c>
       <c r="T20" t="n">
-        <v>1.0911</v>
+        <v>0.8484</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.18</v>
+        <v>-0.9370000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>2.4552</v>
+        <v>1.3252</v>
       </c>
       <c r="W20" t="n">
-        <v>3.5851</v>
+        <v>1.3252</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. BROWN-FERGUSON</t>
+          <t>A. HUELVES GARCIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2533</v>
+        <v>-0.9893999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>1.4772</v>
+        <v>-0.1671</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.7305</v>
+        <v>-0.8223</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6428</v>
+        <v>-2.5241</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8181</v>
+        <v>-2.1655</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1753</v>
+        <v>-0.3586</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2435</v>
+        <v>-1.8043</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4832</v>
+        <v>-1.6147</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7267</v>
+        <v>-0.1896</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8863</v>
+        <v>-0.7197</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3348</v>
+        <v>-0.5508</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5514</v>
+        <v>-0.1689</v>
       </c>
       <c r="P21" t="n">
-        <v>0.87</v>
+        <v>-1.9576</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-3.2626</v>
       </c>
       <c r="R21" t="n">
-        <v>0.87</v>
+        <v>1.305</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9746</v>
+        <v>1.0371</v>
       </c>
       <c r="T21" t="n">
-        <v>1.9732</v>
+        <v>1.3147</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.9986</v>
+        <v>-0.2776</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.4552</v>
+        <v>2.4552</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.7395</v>
+        <v>3.5851</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.7156</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1519</v>
+        <v>-1.1975</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3739</v>
+        <v>0.9327</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.5257</v>
+        <v>-2.1301</v>
       </c>
       <c r="G22" t="n">
         <v>-1.2478</v>
@@ -2170,13 +2170,13 @@
         <v>1.305</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5566</v>
+        <v>0.3978</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2896</v>
+        <v>0.8484</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8462</v>
+        <v>-0.4506</v>
       </c>
       <c r="V22" t="n">
         <v>-0.5649999999999999</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. SEOANE RODICIO</t>
+          <t>J. BROWN-FERGUSON</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6858</v>
+        <v>-1.8494</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6679</v>
+        <v>0.5831</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.0178</v>
+        <v>-2.4325</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.3032</v>
+        <v>-0.6428</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.3988</v>
+        <v>-0.8181</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.9044</v>
+        <v>0.1753</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.2136</v>
+        <v>0.2435</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2039</v>
+        <v>-0.4832</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.4175</v>
+        <v>0.7267</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.0896</v>
+        <v>-0.8863</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.6027</v>
+        <v>-0.3348</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4869</v>
+        <v>-0.5514</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5225</v>
+        <v>0.87</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.0553</v>
+        <v>0.3785</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6044</v>
+        <v>1.0791</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.4508</v>
+        <v>-0.7006</v>
       </c>
       <c r="V23" t="n">
-        <v>1.3252</v>
+        <v>-2.4552</v>
       </c>
       <c r="W23" t="n">
-        <v>1.3252</v>
+        <v>-0.7395</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.7156</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.906</v>
+        <v>-3.7518</v>
       </c>
       <c r="E24" t="n">
         <v>-2.2938</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.6121</v>
+        <v>-1.458</v>
       </c>
       <c r="G24" t="n">
         <v>-0.0017</v>
@@ -2326,13 +2326,13 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0342</v>
+        <v>0.1199</v>
       </c>
       <c r="T24" t="n">
         <v>-0.137</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1027</v>
+        <v>0.2569</v>
       </c>
       <c r="V24" t="n">
         <v>-1.695</v>
@@ -2359,22 +2359,22 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>3.388400000000001</v>
+        <v>4.878600000000002</v>
       </c>
       <c r="E25" t="n">
         <v>10.7973</v>
       </c>
       <c r="F25" t="n">
-        <v>-7.408600000000001</v>
+        <v>-5.9186</v>
       </c>
       <c r="G25" t="n">
-        <v>3.505300000000002</v>
+        <v>3.505300000000001</v>
       </c>
       <c r="H25" t="n">
         <v>-5.7342</v>
       </c>
       <c r="I25" t="n">
-        <v>9.239599999999998</v>
+        <v>9.239599999999999</v>
       </c>
       <c r="J25" t="n">
         <v>11.4797</v>
@@ -2386,10 +2386,10 @@
         <v>14.1086</v>
       </c>
       <c r="M25" t="n">
-        <v>-7.9744</v>
+        <v>-7.974399999999999</v>
       </c>
       <c r="N25" t="n">
-        <v>-3.1054</v>
+        <v>-3.105399999999999</v>
       </c>
       <c r="O25" t="n">
         <v>-4.869</v>
@@ -2404,19 +2404,19 @@
         <v>11.9627</v>
       </c>
       <c r="S25" t="n">
-        <v>4.692699999999999</v>
+        <v>6.1828</v>
       </c>
       <c r="T25" t="n">
-        <v>8.3338</v>
+        <v>8.3339</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.6411</v>
+        <v>-2.1511</v>
       </c>
       <c r="V25" t="n">
         <v>1.7156</v>
       </c>
       <c r="W25" t="n">
-        <v>9.471500000000001</v>
+        <v>9.471499999999999</v>
       </c>
       <c r="X25" t="n">
         <v>-7.7561</v>
